--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>日期</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -75,10 +75,6 @@
   <si>
     <t>SAR</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>每年投入本金</t>
@@ -480,7 +476,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -642,6 +638,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -651,7 +650,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -812,6 +811,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -855,7 +857,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1017,6 +1019,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1026,7 +1031,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1188,6 +1193,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1946497.5998595944</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1987254.1592249498</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1230,7 +1238,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1392,6 +1400,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1401,7 +1412,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1563,6 +1574,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>597129.43630348239</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>637885.9956688378</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1584,11 +1598,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="161442816"/>
-        <c:axId val="161461376"/>
+        <c:axId val="78794112"/>
+        <c:axId val="78804096"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="161442816"/>
+        <c:axId val="78794112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1631,14 +1645,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="161461376"/>
+        <c:crossAx val="78804096"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="161461376"/>
+        <c:axId val="78804096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1689,7 +1703,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="161442816"/>
+        <c:crossAx val="78794112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1880,7 +1894,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2042,6 +2056,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-31695.699802721694</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-41581.258082443448</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2056,8 +2073,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="161500160"/>
-        <c:axId val="161497472"/>
+        <c:axId val="523079680"/>
+        <c:axId val="523068544"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2082,7 +2099,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2244,6 +2261,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2253,7 +2273,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2415,6 +2435,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2431,11 +2454,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="161488896"/>
-        <c:axId val="161491200"/>
+        <c:axId val="523052160"/>
+        <c:axId val="523054080"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="161488896"/>
+        <c:axId val="523052160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2478,14 +2501,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="161491200"/>
+        <c:crossAx val="523054080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="161491200"/>
+        <c:axId val="523054080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2536,12 +2559,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="161488896"/>
+        <c:crossAx val="523052160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="161497472"/>
+        <c:axId val="523068544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2578,12 +2601,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="161500160"/>
+        <c:crossAx val="523079680"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="161500160"/>
+        <c:axId val="523079680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2592,7 +2615,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="161497472"/>
+        <c:crossAx val="523068544"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3001,7 +3024,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -3135,28 +3158,28 @@
       </c>
       <c r="M3" s="8"/>
       <c r="P3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="R3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="S3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="T3" s="15" t="s">
         <v>16</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>17</v>
       </c>
       <c r="U3" s="27" t="s">
         <v>11</v>
       </c>
       <c r="V3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="W3" s="15" t="s">
         <v>18</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>19</v>
       </c>
       <c r="Y3" s="21">
         <v>44561</v>
@@ -5556,6 +5579,47 @@
         <v>180383.67127385744</v>
       </c>
       <c r="M56" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="12.75">
+      <c r="A57" s="11">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="12">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="12">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="13">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="13">
+        <v>-41581.258082443448</v>
+      </c>
+      <c r="F57" s="14">
+        <v>-39080.129391425355</v>
+      </c>
+      <c r="G57" s="14">
+        <v>1659106.4026916635</v>
+      </c>
+      <c r="H57" s="14">
+        <v>1765289.2298686488</v>
+      </c>
+      <c r="I57" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J57" s="14">
+        <v>1987254.1592249498</v>
+      </c>
+      <c r="K57" s="14">
+        <v>637885.9956688378</v>
+      </c>
+      <c r="L57" s="13">
+        <v>221964.92935630088</v>
+      </c>
+      <c r="M57" s="8">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>日期</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -75,6 +75,10 @@
   <si>
     <t>SAR</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>每年投入本金</t>
@@ -476,7 +480,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -641,6 +645,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -650,7 +657,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -814,6 +821,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -857,7 +867,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1022,6 +1032,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1031,7 +1044,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1196,6 +1209,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1987254.1592249498</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2000527.0373446848</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1238,7 +1254,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1403,6 +1419,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1412,7 +1431,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1577,6 +1596,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>637885.9956688378</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>651158.87378857285</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1598,11 +1620,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="78794112"/>
-        <c:axId val="78804096"/>
+        <c:axId val="90645632"/>
+        <c:axId val="90647936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="78794112"/>
+        <c:axId val="90645632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1645,14 +1667,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78804096"/>
+        <c:crossAx val="90647936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="78804096"/>
+        <c:axId val="90647936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1703,7 +1725,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78794112"/>
+        <c:crossAx val="90645632"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1894,7 +1916,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2059,6 +2081,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-41581.258082443448</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-45319.47395988238</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2073,8 +2098,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="523079680"/>
-        <c:axId val="523068544"/>
+        <c:axId val="90743552"/>
+        <c:axId val="90709376"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2099,7 +2124,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2264,6 +2289,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2273,7 +2301,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2438,6 +2466,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2454,11 +2485,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="523052160"/>
-        <c:axId val="523054080"/>
+        <c:axId val="90672512"/>
+        <c:axId val="90707840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="523052160"/>
+        <c:axId val="90672512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2501,14 +2532,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523054080"/>
+        <c:crossAx val="90707840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="523054080"/>
+        <c:axId val="90707840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2559,12 +2590,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523052160"/>
+        <c:crossAx val="90672512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="523068544"/>
+        <c:axId val="90709376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2601,12 +2632,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523079680"/>
+        <c:crossAx val="90743552"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="523079680"/>
+        <c:axId val="90743552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2615,7 +2646,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="523068544"/>
+        <c:crossAx val="90709376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3024,7 +3055,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -3158,28 +3189,28 @@
       </c>
       <c r="M3" s="8"/>
       <c r="P3" s="26" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U3" s="27" t="s">
         <v>11</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y3" s="21">
         <v>44561</v>
@@ -5620,6 +5651,47 @@
         <v>221964.92935630088</v>
       </c>
       <c r="M57" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="12.75">
+      <c r="A58" s="11">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="12">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="12">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="13">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="13">
+        <v>-45319.47395988238</v>
+      </c>
+      <c r="F58" s="14">
+        <v>-42275.627640859449</v>
+      </c>
+      <c r="G58" s="14">
+        <v>1616830.775050804</v>
+      </c>
+      <c r="H58" s="14">
+        <v>1733242.6340285016</v>
+      </c>
+      <c r="I58" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J58" s="14">
+        <v>2000527.0373446848</v>
+      </c>
+      <c r="K58" s="14">
+        <v>651158.87378857285</v>
+      </c>
+      <c r="L58" s="13">
+        <v>267284.40331618325</v>
+      </c>
+      <c r="M58" s="8">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
@@ -480,7 +480,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -648,6 +648,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -657,7 +660,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -824,6 +827,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -867,7 +873,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1035,6 +1041,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1044,7 +1053,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1212,6 +1221,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>2000527.0373446848</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2005377.5635922966</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1254,7 +1266,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1422,6 +1434,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1431,7 +1446,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1599,6 +1614,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>651158.87378857285</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>656009.40003618458</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1620,11 +1638,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="90645632"/>
-        <c:axId val="90647936"/>
+        <c:axId val="36522624"/>
+        <c:axId val="36525952"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90645632"/>
+        <c:axId val="36522624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1667,14 +1685,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90647936"/>
+        <c:crossAx val="36525952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="90647936"/>
+        <c:axId val="36525952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1725,7 +1743,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90645632"/>
+        <c:crossAx val="36522624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1916,7 +1934,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2084,6 +2102,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-45319.47395988238</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-43530.43160834584</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2098,8 +2119,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="90743552"/>
-        <c:axId val="90709376"/>
+        <c:axId val="106026496"/>
+        <c:axId val="106020224"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2124,7 +2145,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2292,6 +2313,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2301,7 +2325,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2469,6 +2493,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2485,11 +2512,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="90672512"/>
-        <c:axId val="90707840"/>
+        <c:axId val="105974400"/>
+        <c:axId val="106018688"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90672512"/>
+        <c:axId val="105974400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2532,14 +2559,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90707840"/>
+        <c:crossAx val="106018688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="90707840"/>
+        <c:axId val="106018688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2590,12 +2617,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90672512"/>
+        <c:crossAx val="105974400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="90709376"/>
+        <c:axId val="106020224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2632,12 +2659,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90743552"/>
+        <c:crossAx val="106026496"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="90743552"/>
+        <c:axId val="106026496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2646,7 +2673,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="90709376"/>
+        <c:crossAx val="106020224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3055,7 +3082,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5695,6 +5722,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="59" spans="1:13" ht="12.75">
+      <c r="A59" s="11">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="12">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="12">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="13">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="13">
+        <v>-43530.43160834584</v>
+      </c>
+      <c r="F59" s="14">
+        <v>-40493.422955785085</v>
+      </c>
+      <c r="G59" s="14">
+        <v>1576337.3520950188</v>
+      </c>
+      <c r="H59" s="14">
+        <v>1694562.7286677675</v>
+      </c>
+      <c r="I59" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J59" s="14">
+        <v>2005377.5635922966</v>
+      </c>
+      <c r="K59" s="14">
+        <v>656009.40003618458</v>
+      </c>
+      <c r="L59" s="13">
+        <v>310814.83492452907</v>
+      </c>
+      <c r="M59" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>日期</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -75,10 +75,6 @@
   <si>
     <t>SAR</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>每年投入本金</t>
@@ -480,7 +476,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -651,6 +647,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -660,7 +659,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -830,6 +829,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -873,7 +875,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1044,6 +1046,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1053,7 +1058,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1224,6 +1229,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>2005377.5635922966</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1962816.3453439225</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1266,7 +1274,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1437,6 +1445,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1446,7 +1457,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1617,6 +1628,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>656009.40003618458</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>613448.18178781052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1638,11 +1652,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="36522624"/>
-        <c:axId val="36525952"/>
+        <c:axId val="78867456"/>
+        <c:axId val="78870016"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="36522624"/>
+        <c:axId val="78867456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1685,14 +1699,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36525952"/>
+        <c:crossAx val="78870016"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="36525952"/>
+        <c:axId val="78870016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1743,7 +1757,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36522624"/>
+        <c:crossAx val="78867456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1934,7 +1948,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2105,6 +2119,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-43530.43160834584</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-34862.836718054765</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2119,8 +2136,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="106026496"/>
-        <c:axId val="106020224"/>
+        <c:axId val="79980032"/>
+        <c:axId val="79969664"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2145,7 +2162,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2316,6 +2333,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2325,7 +2345,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2496,6 +2516,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2512,11 +2535,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="105974400"/>
-        <c:axId val="106018688"/>
+        <c:axId val="79957376"/>
+        <c:axId val="79967744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="105974400"/>
+        <c:axId val="79957376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2559,14 +2582,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="106018688"/>
+        <c:crossAx val="79967744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="106018688"/>
+        <c:axId val="79967744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2617,12 +2640,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="105974400"/>
+        <c:crossAx val="79957376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="106020224"/>
+        <c:axId val="79969664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2659,12 +2682,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="106026496"/>
+        <c:crossAx val="79980032"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="106026496"/>
+        <c:axId val="79980032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2673,7 +2696,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="106020224"/>
+        <c:crossAx val="79969664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3082,7 +3105,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -3216,28 +3239,28 @@
       </c>
       <c r="M3" s="8"/>
       <c r="P3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="R3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="S3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="T3" s="15" t="s">
         <v>16</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>17</v>
       </c>
       <c r="U3" s="27" t="s">
         <v>11</v>
       </c>
       <c r="V3" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="W3" s="15" t="s">
         <v>18</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>19</v>
       </c>
       <c r="Y3" s="21">
         <v>44561</v>
@@ -5760,6 +5783,47 @@
         <v>310814.83492452907</v>
       </c>
       <c r="M59" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="12.75">
+      <c r="A60" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="12">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="12">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="13">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="13">
+        <v>-34862.836718054765</v>
+      </c>
+      <c r="F60" s="14">
+        <v>-33266.066266917558</v>
+      </c>
+      <c r="G60" s="14">
+        <v>1543071.2858281012</v>
+      </c>
+      <c r="H60" s="14">
+        <v>1617138.6737013387</v>
+      </c>
+      <c r="I60" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J60" s="14">
+        <v>1962816.3453439225</v>
+      </c>
+      <c r="K60" s="14">
+        <v>613448.18178781052</v>
+      </c>
+      <c r="L60" s="13">
+        <v>345677.67164258385</v>
+      </c>
+      <c r="M60" s="8">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
@@ -476,7 +476,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -650,6 +650,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -659,7 +662,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -832,6 +835,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -875,7 +881,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1049,6 +1055,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1058,7 +1067,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1232,6 +1241,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1962816.3453439225</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2161872.6456984566</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1274,7 +1286,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1448,6 +1460,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1457,7 +1472,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1631,6 +1646,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>613448.18178781052</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>812504.48214234458</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1652,11 +1670,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="78867456"/>
-        <c:axId val="78870016"/>
+        <c:axId val="344841600"/>
+        <c:axId val="344881792"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="78867456"/>
+        <c:axId val="344841600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1699,14 +1717,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78870016"/>
+        <c:crossAx val="344881792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="78870016"/>
+        <c:axId val="344881792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1757,7 +1775,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78867456"/>
+        <c:crossAx val="344841600"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1948,7 +1966,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2122,6 +2140,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-34862.836718054765</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-65549.847565695833</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2136,8 +2157,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="79980032"/>
-        <c:axId val="79969664"/>
+        <c:axId val="346758144"/>
+        <c:axId val="346756224"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2162,7 +2183,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2336,6 +2357,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2345,7 +2369,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2519,6 +2543,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2535,11 +2562,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="79957376"/>
-        <c:axId val="79967744"/>
+        <c:axId val="345031808"/>
+        <c:axId val="345033728"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="79957376"/>
+        <c:axId val="345031808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2582,14 +2609,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79967744"/>
+        <c:crossAx val="345033728"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79967744"/>
+        <c:axId val="345033728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2640,12 +2667,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79957376"/>
+        <c:crossAx val="345031808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="79969664"/>
+        <c:axId val="346756224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2682,12 +2709,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79980032"/>
+        <c:crossAx val="346758144"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="79980032"/>
+        <c:axId val="346758144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2696,7 +2723,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="79969664"/>
+        <c:crossAx val="346756224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3105,7 +3132,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5827,6 +5854,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="61" spans="1:13" ht="12.75">
+      <c r="A61" s="11">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="12">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="12">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="13">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="13">
+        <v>-65549.847565695833</v>
+      </c>
+      <c r="F61" s="14">
+        <v>-55692.306725832073</v>
+      </c>
+      <c r="G61" s="14">
+        <v>1487378.979102269</v>
+      </c>
+      <c r="H61" s="14">
+        <v>1750645.1264901769</v>
+      </c>
+      <c r="I61" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J61" s="14">
+        <v>2161872.6456984566</v>
+      </c>
+      <c r="K61" s="14">
+        <v>812504.48214234458</v>
+      </c>
+      <c r="L61" s="13">
+        <v>411227.51920827967</v>
+      </c>
+      <c r="M61" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR)cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>日期</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -75,6 +75,10 @@
   <si>
     <t>SAR</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>每年投入本金</t>
@@ -476,7 +480,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -653,6 +657,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -662,7 +669,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -838,6 +845,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -881,7 +891,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1058,6 +1068,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1067,7 +1080,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1244,6 +1257,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>2161872.6456984566</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2263014.35528298</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1286,7 +1302,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1463,6 +1479,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1472,7 +1491,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1649,6 +1668,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>812504.48214234458</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>913646.19172686804</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1670,11 +1692,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="344841600"/>
-        <c:axId val="344881792"/>
+        <c:axId val="401691008"/>
+        <c:axId val="401692928"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="344841600"/>
+        <c:axId val="401691008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1717,14 +1739,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="344881792"/>
+        <c:crossAx val="401692928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="344881792"/>
+        <c:axId val="401692928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1775,7 +1797,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="344841600"/>
+        <c:crossAx val="401691008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1966,7 +1988,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2143,6 +2165,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-65549.847565695833</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-72114.733350567156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2157,8 +2182,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="346758144"/>
-        <c:axId val="346756224"/>
+        <c:axId val="401885056"/>
+        <c:axId val="401883136"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2183,7 +2208,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2360,6 +2385,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2369,7 +2397,7 @@
               <c:f>'模型二 (1)PE副本SAR值非智能计算'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2546,6 +2574,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2562,11 +2593,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="345031808"/>
-        <c:axId val="345033728"/>
+        <c:axId val="401722752"/>
+        <c:axId val="401724928"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="345031808"/>
+        <c:axId val="401722752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2609,14 +2640,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="345033728"/>
+        <c:crossAx val="401724928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="345033728"/>
+        <c:axId val="401724928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2667,12 +2698,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="345031808"/>
+        <c:crossAx val="401722752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="346756224"/>
+        <c:axId val="401883136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2709,12 +2740,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="346758144"/>
+        <c:crossAx val="401885056"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="346758144"/>
+        <c:axId val="401885056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2723,7 +2754,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="346756224"/>
+        <c:crossAx val="401883136"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3132,7 +3163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -3266,28 +3297,28 @@
       </c>
       <c r="M3" s="8"/>
       <c r="P3" s="26" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U3" s="27" t="s">
         <v>11</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y3" s="21">
         <v>44561</v>
@@ -5892,6 +5923,47 @@
         <v>411227.51920827967</v>
       </c>
       <c r="M61" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="12.75">
+      <c r="A62" s="11">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="12">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="12">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="13">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="13">
+        <v>-72114.733350567156</v>
+      </c>
+      <c r="F62" s="14">
+        <v>-57923.480381017253</v>
+      </c>
+      <c r="G62" s="14">
+        <v>1429455.4987212517</v>
+      </c>
+      <c r="H62" s="14">
+        <v>1779672.1027241333</v>
+      </c>
+      <c r="I62" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J62" s="14">
+        <v>2263014.35528298</v>
+      </c>
+      <c r="K62" s="14">
+        <v>913646.19172686804</v>
+      </c>
+      <c r="L62" s="13">
+        <v>483342.25255884684</v>
+      </c>
+      <c r="M62" s="8">
         <v>1</v>
       </c>
     </row>
